--- a/docs/release-schedule.xlsx
+++ b/docs/release-schedule.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Settings" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Schedule!$A$1:$L$244</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Schedule!$A$1:$M$244</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="157">
   <si>
     <t xml:space="preserve">Release #</t>
   </si>
@@ -96,6 +96,9 @@
     <t xml:space="preserve">Notes</t>
   </si>
   <si>
+    <t xml:space="preserve">Created on</t>
+  </si>
+  <si>
     <t xml:space="preserve">A Way Can Be a Guide</t>
   </si>
   <si>
@@ -501,13 +504,28 @@
     <t xml:space="preserve">Next up on</t>
   </si>
   <si>
+    <t xml:space="preserve">Overdue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shorts whose release date has passed and aren't marked Released</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Made, not yet released</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On track?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Behind if anything is overdue. python3 -I pipeline/schedule.py status gives the full report and the buffer.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Legend</t>
   </si>
   <si>
     <t xml:space="preserve">Yellow fill, blue text: inputs you can edit. Black: formulas, don't overwrite.</t>
   </si>
   <si>
-    <t xml:space="preserve">In Schedule, fill in Status, Short title and Notes as you go. Row 2 (Chapter 1 reading) is the worked example.</t>
+    <t xml:space="preserve">In Schedule, Status, Short title, Notes and Created on are filled in as each Short is made (pipeline/schedule.py mark). Row 2 (Chapter 1 reading) is the worked example.</t>
   </si>
   <si>
     <t xml:space="preserve">Chapter titles and source videos come from the channel's archive.org descriptions.</t>
@@ -517,11 +535,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="d\ mmm\ yyyy"/>
     <numFmt numFmtId="166" formatCode="0"/>
     <numFmt numFmtId="167" formatCode="ddd\ d\ mmm\ yyyy"/>
+    <numFmt numFmtId="168" formatCode="@"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -665,7 +684,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -719,6 +738,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1064,7 +1087,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L244"/>
+  <dimension ref="A1:M244"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -1079,6 +1102,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1118,6 +1142,9 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="n">
@@ -1131,10 +1158,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="2" t="str">
         <f aca="false">TEXT(G2,"ddd")</f>
@@ -1146,16 +1173,19 @@
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>46314</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1170,10 +1200,10 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="2" t="str">
         <f aca="false">TEXT(G3,"ddd")</f>
@@ -1188,13 +1218,14 @@
         <v>3</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
+      <c r="M3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="n">
@@ -1208,10 +1239,10 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4" s="2" t="str">
         <f aca="false">TEXT(G4,"ddd")</f>
@@ -1226,13 +1257,14 @@
         <v>2</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
+      <c r="M4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="n">
@@ -1246,10 +1278,10 @@
         <v>2</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" s="2" t="str">
         <f aca="false">TEXT(G5,"ddd")</f>
@@ -1264,14 +1296,17 @@
         <v>2</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>46319</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1286,10 +1321,10 @@
         <v>2</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="2" t="str">
         <f aca="false">TEXT(G6,"ddd")</f>
@@ -1304,13 +1339,14 @@
         <v>3</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
+      <c r="M6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="n">
@@ -1324,10 +1360,10 @@
         <v>2</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="F7" s="2" t="str">
         <f aca="false">TEXT(G7,"ddd")</f>
@@ -1342,13 +1378,14 @@
         <v>2</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
+      <c r="M7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="n">
@@ -1362,10 +1399,10 @@
         <v>3</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F8" s="2" t="str">
         <f aca="false">TEXT(G8,"ddd")</f>
@@ -1380,14 +1417,17 @@
         <v>2</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>46319</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1402,10 +1442,10 @@
         <v>3</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F9" s="2" t="str">
         <f aca="false">TEXT(G9,"ddd")</f>
@@ -1420,13 +1460,14 @@
         <v>3</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
+      <c r="M9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="n">
@@ -1440,10 +1481,10 @@
         <v>3</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F10" s="2" t="str">
         <f aca="false">TEXT(G10,"ddd")</f>
@@ -1458,13 +1499,14 @@
         <v>2</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
+      <c r="M10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="n">
@@ -1478,10 +1520,10 @@
         <v>4</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F11" s="2" t="str">
         <f aca="false">TEXT(G11,"ddd")</f>
@@ -1496,13 +1538,14 @@
         <v>2</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
+      <c r="M11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="n">
@@ -1516,10 +1559,10 @@
         <v>4</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F12" s="2" t="str">
         <f aca="false">TEXT(G12,"ddd")</f>
@@ -1534,13 +1577,14 @@
         <v>3</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
+      <c r="M12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="n">
@@ -1554,10 +1598,10 @@
         <v>4</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F13" s="2" t="str">
         <f aca="false">TEXT(G13,"ddd")</f>
@@ -1572,13 +1616,14 @@
         <v>2</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
+      <c r="M13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="n">
@@ -1592,10 +1637,10 @@
         <v>5</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F14" s="2" t="str">
         <f aca="false">TEXT(G14,"ddd")</f>
@@ -1610,13 +1655,14 @@
         <v>2</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
+      <c r="M14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="n">
@@ -1630,10 +1676,10 @@
         <v>5</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F15" s="2" t="str">
         <f aca="false">TEXT(G15,"ddd")</f>
@@ -1648,13 +1694,14 @@
         <v>3</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
+      <c r="M15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="n">
@@ -1668,10 +1715,10 @@
         <v>5</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F16" s="2" t="str">
         <f aca="false">TEXT(G16,"ddd")</f>
@@ -1686,13 +1733,14 @@
         <v>2</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
+      <c r="M16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="n">
@@ -1706,10 +1754,10 @@
         <v>6</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F17" s="2" t="str">
         <f aca="false">TEXT(G17,"ddd")</f>
@@ -1724,13 +1772,14 @@
         <v>2</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
+      <c r="M17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="n">
@@ -1744,10 +1793,10 @@
         <v>6</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F18" s="2" t="str">
         <f aca="false">TEXT(G18,"ddd")</f>
@@ -1762,13 +1811,14 @@
         <v>3</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
+      <c r="M18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="n">
@@ -1782,10 +1832,10 @@
         <v>6</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F19" s="2" t="str">
         <f aca="false">TEXT(G19,"ddd")</f>
@@ -1800,13 +1850,14 @@
         <v>2</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
+      <c r="M19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="n">
@@ -1820,10 +1871,10 @@
         <v>7</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F20" s="2" t="str">
         <f aca="false">TEXT(G20,"ddd")</f>
@@ -1838,13 +1889,14 @@
         <v>2</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
+      <c r="M20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="n">
@@ -1858,10 +1910,10 @@
         <v>7</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F21" s="2" t="str">
         <f aca="false">TEXT(G21,"ddd")</f>
@@ -1876,13 +1928,14 @@
         <v>3</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
+      <c r="M21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="n">
@@ -1896,10 +1949,10 @@
         <v>7</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F22" s="2" t="str">
         <f aca="false">TEXT(G22,"ddd")</f>
@@ -1914,13 +1967,14 @@
         <v>2</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
+      <c r="M22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="n">
@@ -1934,10 +1988,10 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F23" s="2" t="str">
         <f aca="false">TEXT(G23,"ddd")</f>
@@ -1952,13 +2006,14 @@
         <v>2</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
+      <c r="M23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="n">
@@ -1972,10 +2027,10 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F24" s="2" t="str">
         <f aca="false">TEXT(G24,"ddd")</f>
@@ -1990,13 +2045,14 @@
         <v>3</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
+      <c r="M24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="n">
@@ -2010,10 +2066,10 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F25" s="2" t="str">
         <f aca="false">TEXT(G25,"ddd")</f>
@@ -2028,13 +2084,14 @@
         <v>2</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
+      <c r="M25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="n">
@@ -2048,10 +2105,10 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F26" s="2" t="str">
         <f aca="false">TEXT(G26,"ddd")</f>
@@ -2066,13 +2123,14 @@
         <v>2</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
+      <c r="M26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="n">
@@ -2086,10 +2144,10 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F27" s="2" t="str">
         <f aca="false">TEXT(G27,"ddd")</f>
@@ -2104,13 +2162,14 @@
         <v>3</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
+      <c r="M27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="n">
@@ -2124,10 +2183,10 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F28" s="2" t="str">
         <f aca="false">TEXT(G28,"ddd")</f>
@@ -2142,13 +2201,14 @@
         <v>2</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
+      <c r="M28" s="4"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="n">
@@ -2162,10 +2222,10 @@
         <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F29" s="2" t="str">
         <f aca="false">TEXT(G29,"ddd")</f>
@@ -2180,13 +2240,14 @@
         <v>2</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
+      <c r="M29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="n">
@@ -2200,10 +2261,10 @@
         <v>10</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F30" s="2" t="str">
         <f aca="false">TEXT(G30,"ddd")</f>
@@ -2218,13 +2279,14 @@
         <v>3</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
+      <c r="M30" s="4"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="n">
@@ -2238,10 +2300,10 @@
         <v>10</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F31" s="2" t="str">
         <f aca="false">TEXT(G31,"ddd")</f>
@@ -2256,13 +2318,14 @@
         <v>2</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
+      <c r="M31" s="4"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="n">
@@ -2276,10 +2339,10 @@
         <v>11</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F32" s="2" t="str">
         <f aca="false">TEXT(G32,"ddd")</f>
@@ -2294,13 +2357,14 @@
         <v>2</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
+      <c r="M32" s="4"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="n">
@@ -2314,10 +2378,10 @@
         <v>11</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F33" s="2" t="str">
         <f aca="false">TEXT(G33,"ddd")</f>
@@ -2332,13 +2396,14 @@
         <v>3</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
+      <c r="M33" s="4"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="n">
@@ -2352,10 +2417,10 @@
         <v>11</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F34" s="2" t="str">
         <f aca="false">TEXT(G34,"ddd")</f>
@@ -2370,13 +2435,14 @@
         <v>2</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
+      <c r="M34" s="4"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="n">
@@ -2390,10 +2456,10 @@
         <v>12</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F35" s="2" t="str">
         <f aca="false">TEXT(G35,"ddd")</f>
@@ -2408,13 +2474,14 @@
         <v>2</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
+      <c r="M35" s="4"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="n">
@@ -2428,10 +2495,10 @@
         <v>12</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F36" s="2" t="str">
         <f aca="false">TEXT(G36,"ddd")</f>
@@ -2446,13 +2513,14 @@
         <v>3</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
+      <c r="M36" s="4"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="n">
@@ -2466,10 +2534,10 @@
         <v>12</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F37" s="2" t="str">
         <f aca="false">TEXT(G37,"ddd")</f>
@@ -2484,13 +2552,14 @@
         <v>2</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
+      <c r="M37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="n">
@@ -2504,10 +2573,10 @@
         <v>13</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F38" s="2" t="str">
         <f aca="false">TEXT(G38,"ddd")</f>
@@ -2522,13 +2591,14 @@
         <v>2</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
+      <c r="M38" s="4"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="n">
@@ -2542,10 +2612,10 @@
         <v>13</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F39" s="2" t="str">
         <f aca="false">TEXT(G39,"ddd")</f>
@@ -2560,13 +2630,14 @@
         <v>3</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
+      <c r="M39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="n">
@@ -2580,10 +2651,10 @@
         <v>13</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F40" s="2" t="str">
         <f aca="false">TEXT(G40,"ddd")</f>
@@ -2598,13 +2669,14 @@
         <v>2</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
+      <c r="M40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="n">
@@ -2618,10 +2690,10 @@
         <v>14</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F41" s="2" t="str">
         <f aca="false">TEXT(G41,"ddd")</f>
@@ -2636,13 +2708,14 @@
         <v>2</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
+      <c r="M41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="n">
@@ -2656,10 +2729,10 @@
         <v>14</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F42" s="2" t="str">
         <f aca="false">TEXT(G42,"ddd")</f>
@@ -2674,13 +2747,14 @@
         <v>3</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
+      <c r="M42" s="4"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="n">
@@ -2694,10 +2768,10 @@
         <v>14</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F43" s="2" t="str">
         <f aca="false">TEXT(G43,"ddd")</f>
@@ -2712,13 +2786,14 @@
         <v>2</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
+      <c r="M43" s="4"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="n">
@@ -2732,10 +2807,10 @@
         <v>15</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F44" s="2" t="str">
         <f aca="false">TEXT(G44,"ddd")</f>
@@ -2750,13 +2825,14 @@
         <v>2</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
+      <c r="M44" s="4"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="n">
@@ -2770,10 +2846,10 @@
         <v>15</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F45" s="2" t="str">
         <f aca="false">TEXT(G45,"ddd")</f>
@@ -2788,13 +2864,14 @@
         <v>3</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
+      <c r="M45" s="4"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="n">
@@ -2808,10 +2885,10 @@
         <v>15</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F46" s="2" t="str">
         <f aca="false">TEXT(G46,"ddd")</f>
@@ -2826,13 +2903,14 @@
         <v>2</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
+      <c r="M46" s="4"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="n">
@@ -2846,10 +2924,10 @@
         <v>16</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F47" s="2" t="str">
         <f aca="false">TEXT(G47,"ddd")</f>
@@ -2864,13 +2942,14 @@
         <v>2</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
+      <c r="M47" s="4"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="n">
@@ -2884,10 +2963,10 @@
         <v>16</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F48" s="2" t="str">
         <f aca="false">TEXT(G48,"ddd")</f>
@@ -2902,13 +2981,14 @@
         <v>3</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
+      <c r="M48" s="4"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="n">
@@ -2922,10 +3002,10 @@
         <v>16</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F49" s="2" t="str">
         <f aca="false">TEXT(G49,"ddd")</f>
@@ -2940,13 +3020,14 @@
         <v>2</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
+      <c r="M49" s="4"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="n">
@@ -2960,10 +3041,10 @@
         <v>17</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F50" s="2" t="str">
         <f aca="false">TEXT(G50,"ddd")</f>
@@ -2978,13 +3059,14 @@
         <v>2</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
+      <c r="M50" s="4"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="n">
@@ -2998,10 +3080,10 @@
         <v>17</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F51" s="2" t="str">
         <f aca="false">TEXT(G51,"ddd")</f>
@@ -3016,13 +3098,14 @@
         <v>3</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K51" s="2"/>
       <c r="L51" s="2"/>
+      <c r="M51" s="4"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="n">
@@ -3036,10 +3119,10 @@
         <v>17</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F52" s="2" t="str">
         <f aca="false">TEXT(G52,"ddd")</f>
@@ -3054,13 +3137,14 @@
         <v>2</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
+      <c r="M52" s="4"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="n">
@@ -3074,10 +3158,10 @@
         <v>18</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F53" s="2" t="str">
         <f aca="false">TEXT(G53,"ddd")</f>
@@ -3092,13 +3176,14 @@
         <v>2</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
+      <c r="M53" s="4"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="n">
@@ -3112,10 +3197,10 @@
         <v>18</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F54" s="2" t="str">
         <f aca="false">TEXT(G54,"ddd")</f>
@@ -3130,13 +3215,14 @@
         <v>3</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
+      <c r="M54" s="4"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="n">
@@ -3150,10 +3236,10 @@
         <v>18</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F55" s="2" t="str">
         <f aca="false">TEXT(G55,"ddd")</f>
@@ -3168,13 +3254,14 @@
         <v>2</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
+      <c r="M55" s="4"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="n">
@@ -3188,10 +3275,10 @@
         <v>19</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F56" s="2" t="str">
         <f aca="false">TEXT(G56,"ddd")</f>
@@ -3206,13 +3293,14 @@
         <v>2</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
+      <c r="M56" s="4"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="n">
@@ -3226,10 +3314,10 @@
         <v>19</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F57" s="2" t="str">
         <f aca="false">TEXT(G57,"ddd")</f>
@@ -3244,13 +3332,14 @@
         <v>3</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
+      <c r="M57" s="4"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="n">
@@ -3264,10 +3353,10 @@
         <v>19</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F58" s="2" t="str">
         <f aca="false">TEXT(G58,"ddd")</f>
@@ -3282,13 +3371,14 @@
         <v>2</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
+      <c r="M58" s="4"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="n">
@@ -3302,10 +3392,10 @@
         <v>20</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F59" s="2" t="str">
         <f aca="false">TEXT(G59,"ddd")</f>
@@ -3320,13 +3410,14 @@
         <v>2</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
+      <c r="M59" s="4"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="n">
@@ -3340,10 +3431,10 @@
         <v>20</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F60" s="2" t="str">
         <f aca="false">TEXT(G60,"ddd")</f>
@@ -3358,13 +3449,14 @@
         <v>3</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
+      <c r="M60" s="4"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="n">
@@ -3378,10 +3470,10 @@
         <v>20</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F61" s="2" t="str">
         <f aca="false">TEXT(G61,"ddd")</f>
@@ -3396,13 +3488,14 @@
         <v>2</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
+      <c r="M61" s="4"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="n">
@@ -3416,10 +3509,10 @@
         <v>21</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F62" s="2" t="str">
         <f aca="false">TEXT(G62,"ddd")</f>
@@ -3434,13 +3527,14 @@
         <v>2</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K62" s="2"/>
       <c r="L62" s="2"/>
+      <c r="M62" s="4"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="n">
@@ -3454,10 +3548,10 @@
         <v>21</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F63" s="2" t="str">
         <f aca="false">TEXT(G63,"ddd")</f>
@@ -3472,13 +3566,14 @@
         <v>3</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K63" s="2"/>
       <c r="L63" s="2"/>
+      <c r="M63" s="4"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="n">
@@ -3492,10 +3587,10 @@
         <v>21</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F64" s="2" t="str">
         <f aca="false">TEXT(G64,"ddd")</f>
@@ -3510,13 +3605,14 @@
         <v>2</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K64" s="2"/>
       <c r="L64" s="2"/>
+      <c r="M64" s="4"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="n">
@@ -3530,10 +3626,10 @@
         <v>22</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F65" s="2" t="str">
         <f aca="false">TEXT(G65,"ddd")</f>
@@ -3548,13 +3644,14 @@
         <v>2</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K65" s="2"/>
       <c r="L65" s="2"/>
+      <c r="M65" s="4"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="n">
@@ -3568,10 +3665,10 @@
         <v>22</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F66" s="2" t="str">
         <f aca="false">TEXT(G66,"ddd")</f>
@@ -3586,13 +3683,14 @@
         <v>3</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K66" s="2"/>
       <c r="L66" s="2"/>
+      <c r="M66" s="4"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="n">
@@ -3606,10 +3704,10 @@
         <v>22</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F67" s="2" t="str">
         <f aca="false">TEXT(G67,"ddd")</f>
@@ -3624,13 +3722,14 @@
         <v>2</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K67" s="2"/>
       <c r="L67" s="2"/>
+      <c r="M67" s="4"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="n">
@@ -3644,10 +3743,10 @@
         <v>23</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F68" s="2" t="str">
         <f aca="false">TEXT(G68,"ddd")</f>
@@ -3662,13 +3761,14 @@
         <v>2</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K68" s="2"/>
       <c r="L68" s="2"/>
+      <c r="M68" s="4"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="n">
@@ -3682,10 +3782,10 @@
         <v>23</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F69" s="2" t="str">
         <f aca="false">TEXT(G69,"ddd")</f>
@@ -3700,13 +3800,14 @@
         <v>3</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K69" s="2"/>
       <c r="L69" s="2"/>
+      <c r="M69" s="4"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="n">
@@ -3720,10 +3821,10 @@
         <v>23</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F70" s="2" t="str">
         <f aca="false">TEXT(G70,"ddd")</f>
@@ -3738,13 +3839,14 @@
         <v>2</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K70" s="2"/>
       <c r="L70" s="2"/>
+      <c r="M70" s="4"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="n">
@@ -3758,10 +3860,10 @@
         <v>24</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F71" s="2" t="str">
         <f aca="false">TEXT(G71,"ddd")</f>
@@ -3776,13 +3878,14 @@
         <v>2</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K71" s="2"/>
       <c r="L71" s="2"/>
+      <c r="M71" s="4"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="n">
@@ -3796,10 +3899,10 @@
         <v>24</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F72" s="2" t="str">
         <f aca="false">TEXT(G72,"ddd")</f>
@@ -3814,13 +3917,14 @@
         <v>3</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K72" s="2"/>
       <c r="L72" s="2"/>
+      <c r="M72" s="4"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="n">
@@ -3834,10 +3938,10 @@
         <v>24</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F73" s="2" t="str">
         <f aca="false">TEXT(G73,"ddd")</f>
@@ -3852,13 +3956,14 @@
         <v>2</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K73" s="2"/>
       <c r="L73" s="2"/>
+      <c r="M73" s="4"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="n">
@@ -3872,10 +3977,10 @@
         <v>25</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F74" s="2" t="str">
         <f aca="false">TEXT(G74,"ddd")</f>
@@ -3890,13 +3995,14 @@
         <v>2</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K74" s="2"/>
       <c r="L74" s="2"/>
+      <c r="M74" s="4"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="n">
@@ -3910,10 +4016,10 @@
         <v>25</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F75" s="2" t="str">
         <f aca="false">TEXT(G75,"ddd")</f>
@@ -3928,13 +4034,14 @@
         <v>3</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K75" s="2"/>
       <c r="L75" s="2"/>
+      <c r="M75" s="4"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="n">
@@ -3948,10 +4055,10 @@
         <v>25</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F76" s="2" t="str">
         <f aca="false">TEXT(G76,"ddd")</f>
@@ -3966,13 +4073,14 @@
         <v>2</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K76" s="2"/>
       <c r="L76" s="2"/>
+      <c r="M76" s="4"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="n">
@@ -3986,10 +4094,10 @@
         <v>26</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F77" s="2" t="str">
         <f aca="false">TEXT(G77,"ddd")</f>
@@ -4004,13 +4112,14 @@
         <v>2</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K77" s="2"/>
       <c r="L77" s="2"/>
+      <c r="M77" s="4"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="n">
@@ -4024,10 +4133,10 @@
         <v>26</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F78" s="2" t="str">
         <f aca="false">TEXT(G78,"ddd")</f>
@@ -4042,13 +4151,14 @@
         <v>3</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K78" s="2"/>
       <c r="L78" s="2"/>
+      <c r="M78" s="4"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="n">
@@ -4062,10 +4172,10 @@
         <v>26</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F79" s="2" t="str">
         <f aca="false">TEXT(G79,"ddd")</f>
@@ -4080,13 +4190,14 @@
         <v>2</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K79" s="2"/>
       <c r="L79" s="2"/>
+      <c r="M79" s="4"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="n">
@@ -4100,10 +4211,10 @@
         <v>27</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F80" s="2" t="str">
         <f aca="false">TEXT(G80,"ddd")</f>
@@ -4118,13 +4229,14 @@
         <v>2</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K80" s="2"/>
       <c r="L80" s="2"/>
+      <c r="M80" s="4"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="n">
@@ -4138,10 +4250,10 @@
         <v>27</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F81" s="2" t="str">
         <f aca="false">TEXT(G81,"ddd")</f>
@@ -4156,13 +4268,14 @@
         <v>3</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K81" s="2"/>
       <c r="L81" s="2"/>
+      <c r="M81" s="4"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="n">
@@ -4176,10 +4289,10 @@
         <v>27</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F82" s="2" t="str">
         <f aca="false">TEXT(G82,"ddd")</f>
@@ -4194,13 +4307,14 @@
         <v>2</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K82" s="2"/>
       <c r="L82" s="2"/>
+      <c r="M82" s="4"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2" t="n">
@@ -4214,10 +4328,10 @@
         <v>28</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F83" s="2" t="str">
         <f aca="false">TEXT(G83,"ddd")</f>
@@ -4232,13 +4346,14 @@
         <v>2</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K83" s="2"/>
       <c r="L83" s="2"/>
+      <c r="M83" s="4"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="n">
@@ -4252,10 +4367,10 @@
         <v>28</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F84" s="2" t="str">
         <f aca="false">TEXT(G84,"ddd")</f>
@@ -4270,13 +4385,14 @@
         <v>3</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K84" s="2"/>
       <c r="L84" s="2"/>
+      <c r="M84" s="4"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="n">
@@ -4290,10 +4406,10 @@
         <v>28</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F85" s="2" t="str">
         <f aca="false">TEXT(G85,"ddd")</f>
@@ -4308,13 +4424,14 @@
         <v>2</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K85" s="2"/>
       <c r="L85" s="2"/>
+      <c r="M85" s="4"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="n">
@@ -4328,10 +4445,10 @@
         <v>29</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F86" s="2" t="str">
         <f aca="false">TEXT(G86,"ddd")</f>
@@ -4346,13 +4463,14 @@
         <v>2</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K86" s="2"/>
       <c r="L86" s="2"/>
+      <c r="M86" s="4"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="n">
@@ -4366,10 +4484,10 @@
         <v>29</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F87" s="2" t="str">
         <f aca="false">TEXT(G87,"ddd")</f>
@@ -4384,13 +4502,14 @@
         <v>3</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K87" s="2"/>
       <c r="L87" s="2"/>
+      <c r="M87" s="4"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="n">
@@ -4404,10 +4523,10 @@
         <v>29</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F88" s="2" t="str">
         <f aca="false">TEXT(G88,"ddd")</f>
@@ -4422,13 +4541,14 @@
         <v>2</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K88" s="2"/>
       <c r="L88" s="2"/>
+      <c r="M88" s="4"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="n">
@@ -4442,10 +4562,10 @@
         <v>30</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F89" s="2" t="str">
         <f aca="false">TEXT(G89,"ddd")</f>
@@ -4460,13 +4580,14 @@
         <v>2</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K89" s="2"/>
       <c r="L89" s="2"/>
+      <c r="M89" s="4"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="n">
@@ -4480,10 +4601,10 @@
         <v>30</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F90" s="2" t="str">
         <f aca="false">TEXT(G90,"ddd")</f>
@@ -4498,13 +4619,14 @@
         <v>3</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K90" s="2"/>
       <c r="L90" s="2"/>
+      <c r="M90" s="4"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="n">
@@ -4518,10 +4640,10 @@
         <v>30</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F91" s="2" t="str">
         <f aca="false">TEXT(G91,"ddd")</f>
@@ -4536,13 +4658,14 @@
         <v>2</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K91" s="2"/>
       <c r="L91" s="2"/>
+      <c r="M91" s="4"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="n">
@@ -4556,10 +4679,10 @@
         <v>31</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F92" s="2" t="str">
         <f aca="false">TEXT(G92,"ddd")</f>
@@ -4574,13 +4697,14 @@
         <v>2</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K92" s="2"/>
       <c r="L92" s="2"/>
+      <c r="M92" s="4"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="n">
@@ -4594,10 +4718,10 @@
         <v>31</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F93" s="2" t="str">
         <f aca="false">TEXT(G93,"ddd")</f>
@@ -4612,13 +4736,14 @@
         <v>3</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K93" s="2"/>
       <c r="L93" s="2"/>
+      <c r="M93" s="4"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="n">
@@ -4632,10 +4757,10 @@
         <v>31</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F94" s="2" t="str">
         <f aca="false">TEXT(G94,"ddd")</f>
@@ -4650,13 +4775,14 @@
         <v>2</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K94" s="2"/>
       <c r="L94" s="2"/>
+      <c r="M94" s="4"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="n">
@@ -4670,10 +4796,10 @@
         <v>32</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F95" s="2" t="str">
         <f aca="false">TEXT(G95,"ddd")</f>
@@ -4688,13 +4814,14 @@
         <v>2</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K95" s="2"/>
       <c r="L95" s="2"/>
+      <c r="M95" s="4"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="n">
@@ -4708,10 +4835,10 @@
         <v>32</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F96" s="2" t="str">
         <f aca="false">TEXT(G96,"ddd")</f>
@@ -4726,13 +4853,14 @@
         <v>3</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K96" s="2"/>
       <c r="L96" s="2"/>
+      <c r="M96" s="4"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="n">
@@ -4746,10 +4874,10 @@
         <v>32</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F97" s="2" t="str">
         <f aca="false">TEXT(G97,"ddd")</f>
@@ -4764,13 +4892,14 @@
         <v>2</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K97" s="2"/>
       <c r="L97" s="2"/>
+      <c r="M97" s="4"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="n">
@@ -4784,10 +4913,10 @@
         <v>33</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F98" s="2" t="str">
         <f aca="false">TEXT(G98,"ddd")</f>
@@ -4802,13 +4931,14 @@
         <v>2</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K98" s="2"/>
       <c r="L98" s="2"/>
+      <c r="M98" s="4"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="n">
@@ -4822,10 +4952,10 @@
         <v>33</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F99" s="2" t="str">
         <f aca="false">TEXT(G99,"ddd")</f>
@@ -4840,13 +4970,14 @@
         <v>3</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K99" s="2"/>
       <c r="L99" s="2"/>
+      <c r="M99" s="4"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="n">
@@ -4860,10 +4991,10 @@
         <v>33</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F100" s="2" t="str">
         <f aca="false">TEXT(G100,"ddd")</f>
@@ -4878,13 +5009,14 @@
         <v>2</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K100" s="2"/>
       <c r="L100" s="2"/>
+      <c r="M100" s="4"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="n">
@@ -4898,10 +5030,10 @@
         <v>34</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F101" s="2" t="str">
         <f aca="false">TEXT(G101,"ddd")</f>
@@ -4916,13 +5048,14 @@
         <v>2</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K101" s="2"/>
       <c r="L101" s="2"/>
+      <c r="M101" s="4"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="n">
@@ -4936,10 +5069,10 @@
         <v>34</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F102" s="2" t="str">
         <f aca="false">TEXT(G102,"ddd")</f>
@@ -4954,13 +5087,14 @@
         <v>3</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K102" s="2"/>
       <c r="L102" s="2"/>
+      <c r="M102" s="4"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="n">
@@ -4974,10 +5108,10 @@
         <v>34</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F103" s="2" t="str">
         <f aca="false">TEXT(G103,"ddd")</f>
@@ -4992,13 +5126,14 @@
         <v>2</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K103" s="2"/>
       <c r="L103" s="2"/>
+      <c r="M103" s="4"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="n">
@@ -5012,10 +5147,10 @@
         <v>35</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F104" s="2" t="str">
         <f aca="false">TEXT(G104,"ddd")</f>
@@ -5030,13 +5165,14 @@
         <v>2</v>
       </c>
       <c r="I104" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K104" s="2"/>
       <c r="L104" s="2"/>
+      <c r="M104" s="4"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="n">
@@ -5050,10 +5186,10 @@
         <v>35</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F105" s="2" t="str">
         <f aca="false">TEXT(G105,"ddd")</f>
@@ -5068,13 +5204,14 @@
         <v>3</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K105" s="2"/>
       <c r="L105" s="2"/>
+      <c r="M105" s="4"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="n">
@@ -5088,10 +5225,10 @@
         <v>35</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F106" s="2" t="str">
         <f aca="false">TEXT(G106,"ddd")</f>
@@ -5106,13 +5243,14 @@
         <v>2</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K106" s="2"/>
       <c r="L106" s="2"/>
+      <c r="M106" s="4"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="n">
@@ -5126,10 +5264,10 @@
         <v>36</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F107" s="2" t="str">
         <f aca="false">TEXT(G107,"ddd")</f>
@@ -5144,13 +5282,14 @@
         <v>2</v>
       </c>
       <c r="I107" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K107" s="2"/>
       <c r="L107" s="2"/>
+      <c r="M107" s="4"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="n">
@@ -5164,10 +5303,10 @@
         <v>36</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F108" s="2" t="str">
         <f aca="false">TEXT(G108,"ddd")</f>
@@ -5182,13 +5321,14 @@
         <v>3</v>
       </c>
       <c r="I108" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K108" s="2"/>
       <c r="L108" s="2"/>
+      <c r="M108" s="4"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="n">
@@ -5202,10 +5342,10 @@
         <v>36</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F109" s="2" t="str">
         <f aca="false">TEXT(G109,"ddd")</f>
@@ -5220,13 +5360,14 @@
         <v>2</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K109" s="2"/>
       <c r="L109" s="2"/>
+      <c r="M109" s="4"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="n">
@@ -5240,10 +5381,10 @@
         <v>37</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F110" s="2" t="str">
         <f aca="false">TEXT(G110,"ddd")</f>
@@ -5258,13 +5399,14 @@
         <v>2</v>
       </c>
       <c r="I110" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K110" s="2"/>
       <c r="L110" s="2"/>
+      <c r="M110" s="4"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="2" t="n">
@@ -5278,10 +5420,10 @@
         <v>37</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F111" s="2" t="str">
         <f aca="false">TEXT(G111,"ddd")</f>
@@ -5296,13 +5438,14 @@
         <v>3</v>
       </c>
       <c r="I111" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K111" s="2"/>
       <c r="L111" s="2"/>
+      <c r="M111" s="4"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="2" t="n">
@@ -5316,10 +5459,10 @@
         <v>37</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F112" s="2" t="str">
         <f aca="false">TEXT(G112,"ddd")</f>
@@ -5334,13 +5477,14 @@
         <v>2</v>
       </c>
       <c r="I112" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K112" s="2"/>
       <c r="L112" s="2"/>
+      <c r="M112" s="4"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="2" t="n">
@@ -5354,10 +5498,10 @@
         <v>38</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F113" s="2" t="str">
         <f aca="false">TEXT(G113,"ddd")</f>
@@ -5372,13 +5516,14 @@
         <v>2</v>
       </c>
       <c r="I113" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K113" s="2"/>
       <c r="L113" s="2"/>
+      <c r="M113" s="4"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="n">
@@ -5392,10 +5537,10 @@
         <v>38</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F114" s="2" t="str">
         <f aca="false">TEXT(G114,"ddd")</f>
@@ -5410,13 +5555,14 @@
         <v>3</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K114" s="2"/>
       <c r="L114" s="2"/>
+      <c r="M114" s="4"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="n">
@@ -5430,10 +5576,10 @@
         <v>38</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F115" s="2" t="str">
         <f aca="false">TEXT(G115,"ddd")</f>
@@ -5448,13 +5594,14 @@
         <v>2</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K115" s="2"/>
       <c r="L115" s="2"/>
+      <c r="M115" s="4"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="n">
@@ -5468,10 +5615,10 @@
         <v>39</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F116" s="2" t="str">
         <f aca="false">TEXT(G116,"ddd")</f>
@@ -5486,13 +5633,14 @@
         <v>2</v>
       </c>
       <c r="I116" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K116" s="2"/>
       <c r="L116" s="2"/>
+      <c r="M116" s="4"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="n">
@@ -5506,10 +5654,10 @@
         <v>39</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F117" s="2" t="str">
         <f aca="false">TEXT(G117,"ddd")</f>
@@ -5524,13 +5672,14 @@
         <v>3</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K117" s="2"/>
       <c r="L117" s="2"/>
+      <c r="M117" s="4"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="n">
@@ -5544,10 +5693,10 @@
         <v>39</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F118" s="2" t="str">
         <f aca="false">TEXT(G118,"ddd")</f>
@@ -5562,13 +5711,14 @@
         <v>2</v>
       </c>
       <c r="I118" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K118" s="2"/>
       <c r="L118" s="2"/>
+      <c r="M118" s="4"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="n">
@@ -5582,10 +5732,10 @@
         <v>40</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F119" s="2" t="str">
         <f aca="false">TEXT(G119,"ddd")</f>
@@ -5600,13 +5750,14 @@
         <v>2</v>
       </c>
       <c r="I119" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K119" s="2"/>
       <c r="L119" s="2"/>
+      <c r="M119" s="4"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2" t="n">
@@ -5620,10 +5771,10 @@
         <v>40</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F120" s="2" t="str">
         <f aca="false">TEXT(G120,"ddd")</f>
@@ -5638,13 +5789,14 @@
         <v>3</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K120" s="2"/>
       <c r="L120" s="2"/>
+      <c r="M120" s="4"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="n">
@@ -5658,10 +5810,10 @@
         <v>40</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F121" s="2" t="str">
         <f aca="false">TEXT(G121,"ddd")</f>
@@ -5676,13 +5828,14 @@
         <v>2</v>
       </c>
       <c r="I121" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K121" s="2"/>
       <c r="L121" s="2"/>
+      <c r="M121" s="4"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="n">
@@ -5696,10 +5849,10 @@
         <v>41</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F122" s="2" t="str">
         <f aca="false">TEXT(G122,"ddd")</f>
@@ -5714,13 +5867,14 @@
         <v>2</v>
       </c>
       <c r="I122" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K122" s="2"/>
       <c r="L122" s="2"/>
+      <c r="M122" s="4"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="n">
@@ -5734,10 +5888,10 @@
         <v>41</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F123" s="2" t="str">
         <f aca="false">TEXT(G123,"ddd")</f>
@@ -5752,13 +5906,14 @@
         <v>3</v>
       </c>
       <c r="I123" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K123" s="2"/>
       <c r="L123" s="2"/>
+      <c r="M123" s="4"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2" t="n">
@@ -5772,10 +5927,10 @@
         <v>41</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F124" s="2" t="str">
         <f aca="false">TEXT(G124,"ddd")</f>
@@ -5790,13 +5945,14 @@
         <v>2</v>
       </c>
       <c r="I124" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K124" s="2"/>
       <c r="L124" s="2"/>
+      <c r="M124" s="4"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="n">
@@ -5810,10 +5966,10 @@
         <v>42</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F125" s="2" t="str">
         <f aca="false">TEXT(G125,"ddd")</f>
@@ -5828,13 +5984,14 @@
         <v>2</v>
       </c>
       <c r="I125" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K125" s="2"/>
       <c r="L125" s="2"/>
+      <c r="M125" s="4"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="n">
@@ -5848,10 +6005,10 @@
         <v>42</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F126" s="2" t="str">
         <f aca="false">TEXT(G126,"ddd")</f>
@@ -5866,13 +6023,14 @@
         <v>3</v>
       </c>
       <c r="I126" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K126" s="2"/>
       <c r="L126" s="2"/>
+      <c r="M126" s="4"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="n">
@@ -5886,10 +6044,10 @@
         <v>42</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F127" s="2" t="str">
         <f aca="false">TEXT(G127,"ddd")</f>
@@ -5904,13 +6062,14 @@
         <v>2</v>
       </c>
       <c r="I127" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K127" s="2"/>
       <c r="L127" s="2"/>
+      <c r="M127" s="4"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2" t="n">
@@ -5924,10 +6083,10 @@
         <v>43</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F128" s="2" t="str">
         <f aca="false">TEXT(G128,"ddd")</f>
@@ -5942,13 +6101,14 @@
         <v>2</v>
       </c>
       <c r="I128" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K128" s="2"/>
       <c r="L128" s="2"/>
+      <c r="M128" s="4"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="2" t="n">
@@ -5962,10 +6122,10 @@
         <v>43</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F129" s="2" t="str">
         <f aca="false">TEXT(G129,"ddd")</f>
@@ -5980,13 +6140,14 @@
         <v>3</v>
       </c>
       <c r="I129" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K129" s="2"/>
       <c r="L129" s="2"/>
+      <c r="M129" s="4"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2" t="n">
@@ -6000,10 +6161,10 @@
         <v>43</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F130" s="2" t="str">
         <f aca="false">TEXT(G130,"ddd")</f>
@@ -6018,13 +6179,14 @@
         <v>2</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K130" s="2"/>
       <c r="L130" s="2"/>
+      <c r="M130" s="4"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2" t="n">
@@ -6038,10 +6200,10 @@
         <v>44</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F131" s="2" t="str">
         <f aca="false">TEXT(G131,"ddd")</f>
@@ -6056,13 +6218,14 @@
         <v>2</v>
       </c>
       <c r="I131" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K131" s="2"/>
       <c r="L131" s="2"/>
+      <c r="M131" s="4"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="2" t="n">
@@ -6076,10 +6239,10 @@
         <v>44</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F132" s="2" t="str">
         <f aca="false">TEXT(G132,"ddd")</f>
@@ -6094,13 +6257,14 @@
         <v>3</v>
       </c>
       <c r="I132" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K132" s="2"/>
       <c r="L132" s="2"/>
+      <c r="M132" s="4"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="2" t="n">
@@ -6114,10 +6278,10 @@
         <v>44</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F133" s="2" t="str">
         <f aca="false">TEXT(G133,"ddd")</f>
@@ -6132,13 +6296,14 @@
         <v>2</v>
       </c>
       <c r="I133" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K133" s="2"/>
       <c r="L133" s="2"/>
+      <c r="M133" s="4"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="2" t="n">
@@ -6152,10 +6317,10 @@
         <v>45</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F134" s="2" t="str">
         <f aca="false">TEXT(G134,"ddd")</f>
@@ -6170,13 +6335,14 @@
         <v>2</v>
       </c>
       <c r="I134" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K134" s="2"/>
       <c r="L134" s="2"/>
+      <c r="M134" s="4"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2" t="n">
@@ -6190,10 +6356,10 @@
         <v>45</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F135" s="2" t="str">
         <f aca="false">TEXT(G135,"ddd")</f>
@@ -6208,13 +6374,14 @@
         <v>3</v>
       </c>
       <c r="I135" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J135" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K135" s="2"/>
       <c r="L135" s="2"/>
+      <c r="M135" s="4"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="2" t="n">
@@ -6228,10 +6395,10 @@
         <v>45</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F136" s="2" t="str">
         <f aca="false">TEXT(G136,"ddd")</f>
@@ -6246,13 +6413,14 @@
         <v>2</v>
       </c>
       <c r="I136" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K136" s="2"/>
       <c r="L136" s="2"/>
+      <c r="M136" s="4"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="2" t="n">
@@ -6266,10 +6434,10 @@
         <v>46</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F137" s="2" t="str">
         <f aca="false">TEXT(G137,"ddd")</f>
@@ -6284,13 +6452,14 @@
         <v>2</v>
       </c>
       <c r="I137" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K137" s="2"/>
       <c r="L137" s="2"/>
+      <c r="M137" s="4"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="2" t="n">
@@ -6304,10 +6473,10 @@
         <v>46</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F138" s="2" t="str">
         <f aca="false">TEXT(G138,"ddd")</f>
@@ -6322,13 +6491,14 @@
         <v>3</v>
       </c>
       <c r="I138" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J138" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K138" s="2"/>
       <c r="L138" s="2"/>
+      <c r="M138" s="4"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="n">
@@ -6342,10 +6512,10 @@
         <v>46</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F139" s="2" t="str">
         <f aca="false">TEXT(G139,"ddd")</f>
@@ -6360,13 +6530,14 @@
         <v>2</v>
       </c>
       <c r="I139" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J139" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K139" s="2"/>
       <c r="L139" s="2"/>
+      <c r="M139" s="4"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="n">
@@ -6380,10 +6551,10 @@
         <v>47</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F140" s="2" t="str">
         <f aca="false">TEXT(G140,"ddd")</f>
@@ -6398,13 +6569,14 @@
         <v>2</v>
       </c>
       <c r="I140" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J140" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K140" s="2"/>
       <c r="L140" s="2"/>
+      <c r="M140" s="4"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="2" t="n">
@@ -6418,10 +6590,10 @@
         <v>47</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F141" s="2" t="str">
         <f aca="false">TEXT(G141,"ddd")</f>
@@ -6436,13 +6608,14 @@
         <v>3</v>
       </c>
       <c r="I141" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J141" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K141" s="2"/>
       <c r="L141" s="2"/>
+      <c r="M141" s="4"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="2" t="n">
@@ -6456,10 +6629,10 @@
         <v>47</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F142" s="2" t="str">
         <f aca="false">TEXT(G142,"ddd")</f>
@@ -6474,13 +6647,14 @@
         <v>2</v>
       </c>
       <c r="I142" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J142" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K142" s="2"/>
       <c r="L142" s="2"/>
+      <c r="M142" s="4"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2" t="n">
@@ -6494,10 +6668,10 @@
         <v>48</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F143" s="2" t="str">
         <f aca="false">TEXT(G143,"ddd")</f>
@@ -6512,13 +6686,14 @@
         <v>2</v>
       </c>
       <c r="I143" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J143" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K143" s="2"/>
       <c r="L143" s="2"/>
+      <c r="M143" s="4"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2" t="n">
@@ -6532,10 +6707,10 @@
         <v>48</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F144" s="2" t="str">
         <f aca="false">TEXT(G144,"ddd")</f>
@@ -6550,13 +6725,14 @@
         <v>3</v>
       </c>
       <c r="I144" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J144" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K144" s="2"/>
       <c r="L144" s="2"/>
+      <c r="M144" s="4"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="2" t="n">
@@ -6570,10 +6746,10 @@
         <v>48</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F145" s="2" t="str">
         <f aca="false">TEXT(G145,"ddd")</f>
@@ -6588,13 +6764,14 @@
         <v>2</v>
       </c>
       <c r="I145" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K145" s="2"/>
       <c r="L145" s="2"/>
+      <c r="M145" s="4"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2" t="n">
@@ -6608,10 +6785,10 @@
         <v>49</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F146" s="2" t="str">
         <f aca="false">TEXT(G146,"ddd")</f>
@@ -6626,13 +6803,14 @@
         <v>2</v>
       </c>
       <c r="I146" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J146" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K146" s="2"/>
       <c r="L146" s="2"/>
+      <c r="M146" s="4"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="2" t="n">
@@ -6646,10 +6824,10 @@
         <v>49</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F147" s="2" t="str">
         <f aca="false">TEXT(G147,"ddd")</f>
@@ -6664,13 +6842,14 @@
         <v>3</v>
       </c>
       <c r="I147" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J147" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K147" s="2"/>
       <c r="L147" s="2"/>
+      <c r="M147" s="4"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="2" t="n">
@@ -6684,10 +6863,10 @@
         <v>49</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F148" s="2" t="str">
         <f aca="false">TEXT(G148,"ddd")</f>
@@ -6702,13 +6881,14 @@
         <v>2</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J148" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K148" s="2"/>
       <c r="L148" s="2"/>
+      <c r="M148" s="4"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="2" t="n">
@@ -6722,10 +6902,10 @@
         <v>50</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F149" s="2" t="str">
         <f aca="false">TEXT(G149,"ddd")</f>
@@ -6740,13 +6920,14 @@
         <v>2</v>
       </c>
       <c r="I149" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J149" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K149" s="2"/>
       <c r="L149" s="2"/>
+      <c r="M149" s="4"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2" t="n">
@@ -6760,10 +6941,10 @@
         <v>50</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F150" s="2" t="str">
         <f aca="false">TEXT(G150,"ddd")</f>
@@ -6778,13 +6959,14 @@
         <v>3</v>
       </c>
       <c r="I150" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J150" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K150" s="2"/>
       <c r="L150" s="2"/>
+      <c r="M150" s="4"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="2" t="n">
@@ -6798,10 +6980,10 @@
         <v>50</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F151" s="2" t="str">
         <f aca="false">TEXT(G151,"ddd")</f>
@@ -6816,13 +6998,14 @@
         <v>2</v>
       </c>
       <c r="I151" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J151" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K151" s="2"/>
       <c r="L151" s="2"/>
+      <c r="M151" s="4"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="2" t="n">
@@ -6836,10 +7019,10 @@
         <v>51</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F152" s="2" t="str">
         <f aca="false">TEXT(G152,"ddd")</f>
@@ -6854,13 +7037,14 @@
         <v>2</v>
       </c>
       <c r="I152" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J152" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K152" s="2"/>
       <c r="L152" s="2"/>
+      <c r="M152" s="4"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="2" t="n">
@@ -6874,10 +7058,10 @@
         <v>51</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F153" s="2" t="str">
         <f aca="false">TEXT(G153,"ddd")</f>
@@ -6892,13 +7076,14 @@
         <v>3</v>
       </c>
       <c r="I153" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J153" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K153" s="2"/>
       <c r="L153" s="2"/>
+      <c r="M153" s="4"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="2" t="n">
@@ -6912,10 +7097,10 @@
         <v>51</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F154" s="2" t="str">
         <f aca="false">TEXT(G154,"ddd")</f>
@@ -6930,13 +7115,14 @@
         <v>2</v>
       </c>
       <c r="I154" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J154" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K154" s="2"/>
       <c r="L154" s="2"/>
+      <c r="M154" s="4"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="2" t="n">
@@ -6950,10 +7136,10 @@
         <v>52</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F155" s="2" t="str">
         <f aca="false">TEXT(G155,"ddd")</f>
@@ -6968,13 +7154,14 @@
         <v>2</v>
       </c>
       <c r="I155" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J155" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K155" s="2"/>
       <c r="L155" s="2"/>
+      <c r="M155" s="4"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2" t="n">
@@ -6988,10 +7175,10 @@
         <v>52</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F156" s="2" t="str">
         <f aca="false">TEXT(G156,"ddd")</f>
@@ -7006,13 +7193,14 @@
         <v>3</v>
       </c>
       <c r="I156" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J156" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K156" s="2"/>
       <c r="L156" s="2"/>
+      <c r="M156" s="4"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="2" t="n">
@@ -7026,10 +7214,10 @@
         <v>52</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F157" s="2" t="str">
         <f aca="false">TEXT(G157,"ddd")</f>
@@ -7044,13 +7232,14 @@
         <v>2</v>
       </c>
       <c r="I157" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J157" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K157" s="2"/>
       <c r="L157" s="2"/>
+      <c r="M157" s="4"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2" t="n">
@@ -7064,10 +7253,10 @@
         <v>53</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F158" s="2" t="str">
         <f aca="false">TEXT(G158,"ddd")</f>
@@ -7082,13 +7271,14 @@
         <v>2</v>
       </c>
       <c r="I158" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J158" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K158" s="2"/>
       <c r="L158" s="2"/>
+      <c r="M158" s="4"/>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="2" t="n">
@@ -7102,10 +7292,10 @@
         <v>53</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F159" s="2" t="str">
         <f aca="false">TEXT(G159,"ddd")</f>
@@ -7120,13 +7310,14 @@
         <v>3</v>
       </c>
       <c r="I159" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J159" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K159" s="2"/>
       <c r="L159" s="2"/>
+      <c r="M159" s="4"/>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="2" t="n">
@@ -7140,10 +7331,10 @@
         <v>53</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F160" s="2" t="str">
         <f aca="false">TEXT(G160,"ddd")</f>
@@ -7158,13 +7349,14 @@
         <v>2</v>
       </c>
       <c r="I160" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J160" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K160" s="2"/>
       <c r="L160" s="2"/>
+      <c r="M160" s="4"/>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="2" t="n">
@@ -7178,10 +7370,10 @@
         <v>54</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F161" s="2" t="str">
         <f aca="false">TEXT(G161,"ddd")</f>
@@ -7196,13 +7388,14 @@
         <v>2</v>
       </c>
       <c r="I161" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J161" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K161" s="2"/>
       <c r="L161" s="2"/>
+      <c r="M161" s="4"/>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="2" t="n">
@@ -7216,10 +7409,10 @@
         <v>54</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F162" s="2" t="str">
         <f aca="false">TEXT(G162,"ddd")</f>
@@ -7234,13 +7427,14 @@
         <v>3</v>
       </c>
       <c r="I162" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J162" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K162" s="2"/>
       <c r="L162" s="2"/>
+      <c r="M162" s="4"/>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="2" t="n">
@@ -7254,10 +7448,10 @@
         <v>54</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F163" s="2" t="str">
         <f aca="false">TEXT(G163,"ddd")</f>
@@ -7272,13 +7466,14 @@
         <v>2</v>
       </c>
       <c r="I163" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J163" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K163" s="2"/>
       <c r="L163" s="2"/>
+      <c r="M163" s="4"/>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="2" t="n">
@@ -7292,10 +7487,10 @@
         <v>55</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F164" s="2" t="str">
         <f aca="false">TEXT(G164,"ddd")</f>
@@ -7310,13 +7505,14 @@
         <v>2</v>
       </c>
       <c r="I164" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J164" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K164" s="2"/>
       <c r="L164" s="2"/>
+      <c r="M164" s="4"/>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="2" t="n">
@@ -7330,10 +7526,10 @@
         <v>55</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F165" s="2" t="str">
         <f aca="false">TEXT(G165,"ddd")</f>
@@ -7348,13 +7544,14 @@
         <v>3</v>
       </c>
       <c r="I165" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J165" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K165" s="2"/>
       <c r="L165" s="2"/>
+      <c r="M165" s="4"/>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="2" t="n">
@@ -7368,10 +7565,10 @@
         <v>55</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F166" s="2" t="str">
         <f aca="false">TEXT(G166,"ddd")</f>
@@ -7386,13 +7583,14 @@
         <v>2</v>
       </c>
       <c r="I166" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J166" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K166" s="2"/>
       <c r="L166" s="2"/>
+      <c r="M166" s="4"/>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="2" t="n">
@@ -7406,10 +7604,10 @@
         <v>56</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F167" s="2" t="str">
         <f aca="false">TEXT(G167,"ddd")</f>
@@ -7424,13 +7622,14 @@
         <v>2</v>
       </c>
       <c r="I167" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J167" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K167" s="2"/>
       <c r="L167" s="2"/>
+      <c r="M167" s="4"/>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="2" t="n">
@@ -7444,10 +7643,10 @@
         <v>56</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F168" s="2" t="str">
         <f aca="false">TEXT(G168,"ddd")</f>
@@ -7462,13 +7661,14 @@
         <v>3</v>
       </c>
       <c r="I168" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J168" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K168" s="2"/>
       <c r="L168" s="2"/>
+      <c r="M168" s="4"/>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="2" t="n">
@@ -7482,10 +7682,10 @@
         <v>56</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F169" s="2" t="str">
         <f aca="false">TEXT(G169,"ddd")</f>
@@ -7500,13 +7700,14 @@
         <v>2</v>
       </c>
       <c r="I169" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J169" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K169" s="2"/>
       <c r="L169" s="2"/>
+      <c r="M169" s="4"/>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="2" t="n">
@@ -7520,10 +7721,10 @@
         <v>57</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F170" s="2" t="str">
         <f aca="false">TEXT(G170,"ddd")</f>
@@ -7538,13 +7739,14 @@
         <v>2</v>
       </c>
       <c r="I170" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J170" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K170" s="2"/>
       <c r="L170" s="2"/>
+      <c r="M170" s="4"/>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="2" t="n">
@@ -7558,10 +7760,10 @@
         <v>57</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F171" s="2" t="str">
         <f aca="false">TEXT(G171,"ddd")</f>
@@ -7576,13 +7778,14 @@
         <v>3</v>
       </c>
       <c r="I171" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J171" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K171" s="2"/>
       <c r="L171" s="2"/>
+      <c r="M171" s="4"/>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="2" t="n">
@@ -7596,10 +7799,10 @@
         <v>57</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F172" s="2" t="str">
         <f aca="false">TEXT(G172,"ddd")</f>
@@ -7614,13 +7817,14 @@
         <v>2</v>
       </c>
       <c r="I172" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J172" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K172" s="2"/>
       <c r="L172" s="2"/>
+      <c r="M172" s="4"/>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="2" t="n">
@@ -7634,10 +7838,10 @@
         <v>58</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F173" s="2" t="str">
         <f aca="false">TEXT(G173,"ddd")</f>
@@ -7652,13 +7856,14 @@
         <v>2</v>
       </c>
       <c r="I173" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J173" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K173" s="2"/>
       <c r="L173" s="2"/>
+      <c r="M173" s="4"/>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="2" t="n">
@@ -7672,10 +7877,10 @@
         <v>58</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F174" s="2" t="str">
         <f aca="false">TEXT(G174,"ddd")</f>
@@ -7690,13 +7895,14 @@
         <v>3</v>
       </c>
       <c r="I174" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J174" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K174" s="2"/>
       <c r="L174" s="2"/>
+      <c r="M174" s="4"/>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="2" t="n">
@@ -7710,10 +7916,10 @@
         <v>58</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F175" s="2" t="str">
         <f aca="false">TEXT(G175,"ddd")</f>
@@ -7728,13 +7934,14 @@
         <v>2</v>
       </c>
       <c r="I175" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J175" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K175" s="2"/>
       <c r="L175" s="2"/>
+      <c r="M175" s="4"/>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="2" t="n">
@@ -7748,10 +7955,10 @@
         <v>59</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F176" s="2" t="str">
         <f aca="false">TEXT(G176,"ddd")</f>
@@ -7766,13 +7973,14 @@
         <v>2</v>
       </c>
       <c r="I176" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J176" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K176" s="2"/>
       <c r="L176" s="2"/>
+      <c r="M176" s="4"/>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="2" t="n">
@@ -7786,10 +7994,10 @@
         <v>59</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F177" s="2" t="str">
         <f aca="false">TEXT(G177,"ddd")</f>
@@ -7804,13 +8012,14 @@
         <v>3</v>
       </c>
       <c r="I177" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J177" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K177" s="2"/>
       <c r="L177" s="2"/>
+      <c r="M177" s="4"/>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="2" t="n">
@@ -7824,10 +8033,10 @@
         <v>59</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F178" s="2" t="str">
         <f aca="false">TEXT(G178,"ddd")</f>
@@ -7842,13 +8051,14 @@
         <v>2</v>
       </c>
       <c r="I178" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J178" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K178" s="2"/>
       <c r="L178" s="2"/>
+      <c r="M178" s="4"/>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="2" t="n">
@@ -7862,10 +8072,10 @@
         <v>60</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F179" s="2" t="str">
         <f aca="false">TEXT(G179,"ddd")</f>
@@ -7880,13 +8090,14 @@
         <v>2</v>
       </c>
       <c r="I179" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J179" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K179" s="2"/>
       <c r="L179" s="2"/>
+      <c r="M179" s="4"/>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="2" t="n">
@@ -7900,10 +8111,10 @@
         <v>60</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F180" s="2" t="str">
         <f aca="false">TEXT(G180,"ddd")</f>
@@ -7918,13 +8129,14 @@
         <v>3</v>
       </c>
       <c r="I180" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J180" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K180" s="2"/>
       <c r="L180" s="2"/>
+      <c r="M180" s="4"/>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="2" t="n">
@@ -7938,10 +8150,10 @@
         <v>60</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F181" s="2" t="str">
         <f aca="false">TEXT(G181,"ddd")</f>
@@ -7956,13 +8168,14 @@
         <v>2</v>
       </c>
       <c r="I181" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J181" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K181" s="2"/>
       <c r="L181" s="2"/>
+      <c r="M181" s="4"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="2" t="n">
@@ -7976,10 +8189,10 @@
         <v>61</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F182" s="2" t="str">
         <f aca="false">TEXT(G182,"ddd")</f>
@@ -7994,13 +8207,14 @@
         <v>2</v>
       </c>
       <c r="I182" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J182" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K182" s="2"/>
       <c r="L182" s="2"/>
+      <c r="M182" s="4"/>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="2" t="n">
@@ -8014,10 +8228,10 @@
         <v>61</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F183" s="2" t="str">
         <f aca="false">TEXT(G183,"ddd")</f>
@@ -8032,13 +8246,14 @@
         <v>3</v>
       </c>
       <c r="I183" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J183" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K183" s="2"/>
       <c r="L183" s="2"/>
+      <c r="M183" s="4"/>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="2" t="n">
@@ -8052,10 +8267,10 @@
         <v>61</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F184" s="2" t="str">
         <f aca="false">TEXT(G184,"ddd")</f>
@@ -8070,13 +8285,14 @@
         <v>2</v>
       </c>
       <c r="I184" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J184" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K184" s="2"/>
       <c r="L184" s="2"/>
+      <c r="M184" s="4"/>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="2" t="n">
@@ -8090,10 +8306,10 @@
         <v>62</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F185" s="2" t="str">
         <f aca="false">TEXT(G185,"ddd")</f>
@@ -8108,13 +8324,14 @@
         <v>2</v>
       </c>
       <c r="I185" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J185" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K185" s="2"/>
       <c r="L185" s="2"/>
+      <c r="M185" s="4"/>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="2" t="n">
@@ -8128,10 +8345,10 @@
         <v>62</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F186" s="2" t="str">
         <f aca="false">TEXT(G186,"ddd")</f>
@@ -8146,13 +8363,14 @@
         <v>3</v>
       </c>
       <c r="I186" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J186" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K186" s="2"/>
       <c r="L186" s="2"/>
+      <c r="M186" s="4"/>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="2" t="n">
@@ -8166,10 +8384,10 @@
         <v>62</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F187" s="2" t="str">
         <f aca="false">TEXT(G187,"ddd")</f>
@@ -8184,13 +8402,14 @@
         <v>2</v>
       </c>
       <c r="I187" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J187" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K187" s="2"/>
       <c r="L187" s="2"/>
+      <c r="M187" s="4"/>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="2" t="n">
@@ -8204,10 +8423,10 @@
         <v>63</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F188" s="2" t="str">
         <f aca="false">TEXT(G188,"ddd")</f>
@@ -8222,13 +8441,14 @@
         <v>2</v>
       </c>
       <c r="I188" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J188" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K188" s="2"/>
       <c r="L188" s="2"/>
+      <c r="M188" s="4"/>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="2" t="n">
@@ -8242,10 +8462,10 @@
         <v>63</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F189" s="2" t="str">
         <f aca="false">TEXT(G189,"ddd")</f>
@@ -8260,13 +8480,14 @@
         <v>3</v>
       </c>
       <c r="I189" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J189" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K189" s="2"/>
       <c r="L189" s="2"/>
+      <c r="M189" s="4"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="2" t="n">
@@ -8280,10 +8501,10 @@
         <v>63</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F190" s="2" t="str">
         <f aca="false">TEXT(G190,"ddd")</f>
@@ -8298,13 +8519,14 @@
         <v>2</v>
       </c>
       <c r="I190" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J190" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K190" s="2"/>
       <c r="L190" s="2"/>
+      <c r="M190" s="4"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="2" t="n">
@@ -8318,10 +8540,10 @@
         <v>64</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F191" s="2" t="str">
         <f aca="false">TEXT(G191,"ddd")</f>
@@ -8336,13 +8558,14 @@
         <v>2</v>
       </c>
       <c r="I191" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J191" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K191" s="2"/>
       <c r="L191" s="2"/>
+      <c r="M191" s="4"/>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="2" t="n">
@@ -8356,10 +8579,10 @@
         <v>64</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F192" s="2" t="str">
         <f aca="false">TEXT(G192,"ddd")</f>
@@ -8374,13 +8597,14 @@
         <v>3</v>
       </c>
       <c r="I192" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J192" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K192" s="2"/>
       <c r="L192" s="2"/>
+      <c r="M192" s="4"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="2" t="n">
@@ -8394,10 +8618,10 @@
         <v>64</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F193" s="2" t="str">
         <f aca="false">TEXT(G193,"ddd")</f>
@@ -8412,13 +8636,14 @@
         <v>2</v>
       </c>
       <c r="I193" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J193" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K193" s="2"/>
       <c r="L193" s="2"/>
+      <c r="M193" s="4"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="2" t="n">
@@ -8432,10 +8657,10 @@
         <v>65</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F194" s="2" t="str">
         <f aca="false">TEXT(G194,"ddd")</f>
@@ -8450,13 +8675,14 @@
         <v>2</v>
       </c>
       <c r="I194" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J194" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K194" s="2"/>
       <c r="L194" s="2"/>
+      <c r="M194" s="4"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="2" t="n">
@@ -8470,10 +8696,10 @@
         <v>65</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F195" s="2" t="str">
         <f aca="false">TEXT(G195,"ddd")</f>
@@ -8488,13 +8714,14 @@
         <v>3</v>
       </c>
       <c r="I195" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J195" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K195" s="2"/>
       <c r="L195" s="2"/>
+      <c r="M195" s="4"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="2" t="n">
@@ -8508,10 +8735,10 @@
         <v>65</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F196" s="2" t="str">
         <f aca="false">TEXT(G196,"ddd")</f>
@@ -8526,13 +8753,14 @@
         <v>2</v>
       </c>
       <c r="I196" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J196" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K196" s="2"/>
       <c r="L196" s="2"/>
+      <c r="M196" s="4"/>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="2" t="n">
@@ -8546,10 +8774,10 @@
         <v>66</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F197" s="2" t="str">
         <f aca="false">TEXT(G197,"ddd")</f>
@@ -8564,13 +8792,14 @@
         <v>2</v>
       </c>
       <c r="I197" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J197" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K197" s="2"/>
       <c r="L197" s="2"/>
+      <c r="M197" s="4"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="2" t="n">
@@ -8584,10 +8813,10 @@
         <v>66</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F198" s="2" t="str">
         <f aca="false">TEXT(G198,"ddd")</f>
@@ -8602,13 +8831,14 @@
         <v>3</v>
       </c>
       <c r="I198" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J198" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K198" s="2"/>
       <c r="L198" s="2"/>
+      <c r="M198" s="4"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="2" t="n">
@@ -8622,10 +8852,10 @@
         <v>66</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F199" s="2" t="str">
         <f aca="false">TEXT(G199,"ddd")</f>
@@ -8640,13 +8870,14 @@
         <v>2</v>
       </c>
       <c r="I199" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J199" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K199" s="2"/>
       <c r="L199" s="2"/>
+      <c r="M199" s="4"/>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="2" t="n">
@@ -8660,10 +8891,10 @@
         <v>67</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F200" s="2" t="str">
         <f aca="false">TEXT(G200,"ddd")</f>
@@ -8678,13 +8909,14 @@
         <v>2</v>
       </c>
       <c r="I200" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J200" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K200" s="2"/>
       <c r="L200" s="2"/>
+      <c r="M200" s="4"/>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="2" t="n">
@@ -8698,10 +8930,10 @@
         <v>67</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F201" s="2" t="str">
         <f aca="false">TEXT(G201,"ddd")</f>
@@ -8716,13 +8948,14 @@
         <v>3</v>
       </c>
       <c r="I201" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J201" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K201" s="2"/>
       <c r="L201" s="2"/>
+      <c r="M201" s="4"/>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="2" t="n">
@@ -8736,10 +8969,10 @@
         <v>67</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F202" s="2" t="str">
         <f aca="false">TEXT(G202,"ddd")</f>
@@ -8754,13 +8987,14 @@
         <v>2</v>
       </c>
       <c r="I202" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J202" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K202" s="2"/>
       <c r="L202" s="2"/>
+      <c r="M202" s="4"/>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="2" t="n">
@@ -8774,10 +9008,10 @@
         <v>68</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F203" s="2" t="str">
         <f aca="false">TEXT(G203,"ddd")</f>
@@ -8792,13 +9026,14 @@
         <v>2</v>
       </c>
       <c r="I203" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J203" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K203" s="2"/>
       <c r="L203" s="2"/>
+      <c r="M203" s="4"/>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="2" t="n">
@@ -8812,10 +9047,10 @@
         <v>68</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F204" s="2" t="str">
         <f aca="false">TEXT(G204,"ddd")</f>
@@ -8830,13 +9065,14 @@
         <v>3</v>
       </c>
       <c r="I204" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J204" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K204" s="2"/>
       <c r="L204" s="2"/>
+      <c r="M204" s="4"/>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="2" t="n">
@@ -8850,10 +9086,10 @@
         <v>68</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F205" s="2" t="str">
         <f aca="false">TEXT(G205,"ddd")</f>
@@ -8868,13 +9104,14 @@
         <v>2</v>
       </c>
       <c r="I205" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J205" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K205" s="2"/>
       <c r="L205" s="2"/>
+      <c r="M205" s="4"/>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="2" t="n">
@@ -8888,10 +9125,10 @@
         <v>69</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F206" s="2" t="str">
         <f aca="false">TEXT(G206,"ddd")</f>
@@ -8906,13 +9143,14 @@
         <v>2</v>
       </c>
       <c r="I206" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J206" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K206" s="2"/>
       <c r="L206" s="2"/>
+      <c r="M206" s="4"/>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="2" t="n">
@@ -8926,10 +9164,10 @@
         <v>69</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F207" s="2" t="str">
         <f aca="false">TEXT(G207,"ddd")</f>
@@ -8944,13 +9182,14 @@
         <v>3</v>
       </c>
       <c r="I207" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J207" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K207" s="2"/>
       <c r="L207" s="2"/>
+      <c r="M207" s="4"/>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="2" t="n">
@@ -8964,10 +9203,10 @@
         <v>69</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F208" s="2" t="str">
         <f aca="false">TEXT(G208,"ddd")</f>
@@ -8982,13 +9221,14 @@
         <v>2</v>
       </c>
       <c r="I208" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J208" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K208" s="2"/>
       <c r="L208" s="2"/>
+      <c r="M208" s="4"/>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="2" t="n">
@@ -9002,10 +9242,10 @@
         <v>70</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F209" s="2" t="str">
         <f aca="false">TEXT(G209,"ddd")</f>
@@ -9020,13 +9260,14 @@
         <v>2</v>
       </c>
       <c r="I209" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J209" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K209" s="2"/>
       <c r="L209" s="2"/>
+      <c r="M209" s="4"/>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="2" t="n">
@@ -9040,10 +9281,10 @@
         <v>70</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F210" s="2" t="str">
         <f aca="false">TEXT(G210,"ddd")</f>
@@ -9058,13 +9299,14 @@
         <v>3</v>
       </c>
       <c r="I210" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J210" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K210" s="2"/>
       <c r="L210" s="2"/>
+      <c r="M210" s="4"/>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="2" t="n">
@@ -9078,10 +9320,10 @@
         <v>70</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F211" s="2" t="str">
         <f aca="false">TEXT(G211,"ddd")</f>
@@ -9096,13 +9338,14 @@
         <v>2</v>
       </c>
       <c r="I211" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J211" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K211" s="2"/>
       <c r="L211" s="2"/>
+      <c r="M211" s="4"/>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="2" t="n">
@@ -9116,10 +9359,10 @@
         <v>71</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F212" s="2" t="str">
         <f aca="false">TEXT(G212,"ddd")</f>
@@ -9134,13 +9377,14 @@
         <v>2</v>
       </c>
       <c r="I212" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J212" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K212" s="2"/>
       <c r="L212" s="2"/>
+      <c r="M212" s="4"/>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="2" t="n">
@@ -9154,10 +9398,10 @@
         <v>71</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F213" s="2" t="str">
         <f aca="false">TEXT(G213,"ddd")</f>
@@ -9172,13 +9416,14 @@
         <v>3</v>
       </c>
       <c r="I213" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J213" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K213" s="2"/>
       <c r="L213" s="2"/>
+      <c r="M213" s="4"/>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="2" t="n">
@@ -9192,10 +9437,10 @@
         <v>71</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F214" s="2" t="str">
         <f aca="false">TEXT(G214,"ddd")</f>
@@ -9210,13 +9455,14 @@
         <v>2</v>
       </c>
       <c r="I214" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J214" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K214" s="2"/>
       <c r="L214" s="2"/>
+      <c r="M214" s="4"/>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="2" t="n">
@@ -9230,10 +9476,10 @@
         <v>72</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F215" s="2" t="str">
         <f aca="false">TEXT(G215,"ddd")</f>
@@ -9248,13 +9494,14 @@
         <v>2</v>
       </c>
       <c r="I215" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J215" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K215" s="2"/>
       <c r="L215" s="2"/>
+      <c r="M215" s="4"/>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="2" t="n">
@@ -9268,10 +9515,10 @@
         <v>72</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F216" s="2" t="str">
         <f aca="false">TEXT(G216,"ddd")</f>
@@ -9286,13 +9533,14 @@
         <v>3</v>
       </c>
       <c r="I216" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J216" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K216" s="2"/>
       <c r="L216" s="2"/>
+      <c r="M216" s="4"/>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="2" t="n">
@@ -9306,10 +9554,10 @@
         <v>72</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F217" s="2" t="str">
         <f aca="false">TEXT(G217,"ddd")</f>
@@ -9324,13 +9572,14 @@
         <v>2</v>
       </c>
       <c r="I217" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J217" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K217" s="2"/>
       <c r="L217" s="2"/>
+      <c r="M217" s="4"/>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="2" t="n">
@@ -9344,10 +9593,10 @@
         <v>73</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F218" s="2" t="str">
         <f aca="false">TEXT(G218,"ddd")</f>
@@ -9362,13 +9611,14 @@
         <v>2</v>
       </c>
       <c r="I218" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J218" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K218" s="2"/>
       <c r="L218" s="2"/>
+      <c r="M218" s="4"/>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="2" t="n">
@@ -9382,10 +9632,10 @@
         <v>73</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F219" s="2" t="str">
         <f aca="false">TEXT(G219,"ddd")</f>
@@ -9400,13 +9650,14 @@
         <v>3</v>
       </c>
       <c r="I219" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J219" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K219" s="2"/>
       <c r="L219" s="2"/>
+      <c r="M219" s="4"/>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="2" t="n">
@@ -9420,10 +9671,10 @@
         <v>73</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F220" s="2" t="str">
         <f aca="false">TEXT(G220,"ddd")</f>
@@ -9438,13 +9689,14 @@
         <v>2</v>
       </c>
       <c r="I220" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J220" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K220" s="2"/>
       <c r="L220" s="2"/>
+      <c r="M220" s="4"/>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="2" t="n">
@@ -9458,10 +9710,10 @@
         <v>74</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F221" s="2" t="str">
         <f aca="false">TEXT(G221,"ddd")</f>
@@ -9476,13 +9728,14 @@
         <v>2</v>
       </c>
       <c r="I221" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J221" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K221" s="2"/>
       <c r="L221" s="2"/>
+      <c r="M221" s="4"/>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="2" t="n">
@@ -9496,10 +9749,10 @@
         <v>74</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F222" s="2" t="str">
         <f aca="false">TEXT(G222,"ddd")</f>
@@ -9514,13 +9767,14 @@
         <v>3</v>
       </c>
       <c r="I222" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J222" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K222" s="2"/>
       <c r="L222" s="2"/>
+      <c r="M222" s="4"/>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="2" t="n">
@@ -9534,10 +9788,10 @@
         <v>74</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F223" s="2" t="str">
         <f aca="false">TEXT(G223,"ddd")</f>
@@ -9552,13 +9806,14 @@
         <v>2</v>
       </c>
       <c r="I223" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J223" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K223" s="2"/>
       <c r="L223" s="2"/>
+      <c r="M223" s="4"/>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="2" t="n">
@@ -9572,10 +9827,10 @@
         <v>75</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F224" s="2" t="str">
         <f aca="false">TEXT(G224,"ddd")</f>
@@ -9590,13 +9845,14 @@
         <v>2</v>
       </c>
       <c r="I224" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J224" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K224" s="2"/>
       <c r="L224" s="2"/>
+      <c r="M224" s="4"/>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="2" t="n">
@@ -9610,10 +9866,10 @@
         <v>75</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F225" s="2" t="str">
         <f aca="false">TEXT(G225,"ddd")</f>
@@ -9628,13 +9884,14 @@
         <v>3</v>
       </c>
       <c r="I225" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J225" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K225" s="2"/>
       <c r="L225" s="2"/>
+      <c r="M225" s="4"/>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="2" t="n">
@@ -9648,10 +9905,10 @@
         <v>75</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F226" s="2" t="str">
         <f aca="false">TEXT(G226,"ddd")</f>
@@ -9666,13 +9923,14 @@
         <v>2</v>
       </c>
       <c r="I226" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J226" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K226" s="2"/>
       <c r="L226" s="2"/>
+      <c r="M226" s="4"/>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="2" t="n">
@@ -9686,10 +9944,10 @@
         <v>76</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F227" s="2" t="str">
         <f aca="false">TEXT(G227,"ddd")</f>
@@ -9704,13 +9962,14 @@
         <v>2</v>
       </c>
       <c r="I227" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J227" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K227" s="2"/>
       <c r="L227" s="2"/>
+      <c r="M227" s="4"/>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="2" t="n">
@@ -9724,10 +9983,10 @@
         <v>76</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F228" s="2" t="str">
         <f aca="false">TEXT(G228,"ddd")</f>
@@ -9742,13 +10001,14 @@
         <v>3</v>
       </c>
       <c r="I228" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J228" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K228" s="2"/>
       <c r="L228" s="2"/>
+      <c r="M228" s="4"/>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="2" t="n">
@@ -9762,10 +10022,10 @@
         <v>76</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F229" s="2" t="str">
         <f aca="false">TEXT(G229,"ddd")</f>
@@ -9780,13 +10040,14 @@
         <v>2</v>
       </c>
       <c r="I229" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J229" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K229" s="2"/>
       <c r="L229" s="2"/>
+      <c r="M229" s="4"/>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="2" t="n">
@@ -9800,10 +10061,10 @@
         <v>77</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F230" s="2" t="str">
         <f aca="false">TEXT(G230,"ddd")</f>
@@ -9818,13 +10079,14 @@
         <v>2</v>
       </c>
       <c r="I230" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J230" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K230" s="2"/>
       <c r="L230" s="2"/>
+      <c r="M230" s="4"/>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="2" t="n">
@@ -9838,10 +10100,10 @@
         <v>77</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F231" s="2" t="str">
         <f aca="false">TEXT(G231,"ddd")</f>
@@ -9856,13 +10118,14 @@
         <v>3</v>
       </c>
       <c r="I231" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J231" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K231" s="2"/>
       <c r="L231" s="2"/>
+      <c r="M231" s="4"/>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="2" t="n">
@@ -9876,10 +10139,10 @@
         <v>77</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F232" s="2" t="str">
         <f aca="false">TEXT(G232,"ddd")</f>
@@ -9894,13 +10157,14 @@
         <v>2</v>
       </c>
       <c r="I232" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J232" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K232" s="2"/>
       <c r="L232" s="2"/>
+      <c r="M232" s="4"/>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="2" t="n">
@@ -9914,10 +10178,10 @@
         <v>78</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F233" s="2" t="str">
         <f aca="false">TEXT(G233,"ddd")</f>
@@ -9932,13 +10196,14 @@
         <v>2</v>
       </c>
       <c r="I233" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J233" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K233" s="2"/>
       <c r="L233" s="2"/>
+      <c r="M233" s="4"/>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="2" t="n">
@@ -9952,10 +10217,10 @@
         <v>78</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F234" s="2" t="str">
         <f aca="false">TEXT(G234,"ddd")</f>
@@ -9970,13 +10235,14 @@
         <v>3</v>
       </c>
       <c r="I234" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J234" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K234" s="2"/>
       <c r="L234" s="2"/>
+      <c r="M234" s="4"/>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="2" t="n">
@@ -9990,10 +10256,10 @@
         <v>78</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F235" s="2" t="str">
         <f aca="false">TEXT(G235,"ddd")</f>
@@ -10008,13 +10274,14 @@
         <v>2</v>
       </c>
       <c r="I235" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J235" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K235" s="2"/>
       <c r="L235" s="2"/>
+      <c r="M235" s="4"/>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="2" t="n">
@@ -10028,10 +10295,10 @@
         <v>79</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F236" s="2" t="str">
         <f aca="false">TEXT(G236,"ddd")</f>
@@ -10046,13 +10313,14 @@
         <v>2</v>
       </c>
       <c r="I236" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J236" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K236" s="2"/>
       <c r="L236" s="2"/>
+      <c r="M236" s="4"/>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="2" t="n">
@@ -10066,10 +10334,10 @@
         <v>79</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F237" s="2" t="str">
         <f aca="false">TEXT(G237,"ddd")</f>
@@ -10084,13 +10352,14 @@
         <v>3</v>
       </c>
       <c r="I237" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J237" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K237" s="2"/>
       <c r="L237" s="2"/>
+      <c r="M237" s="4"/>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="2" t="n">
@@ -10104,10 +10373,10 @@
         <v>79</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F238" s="2" t="str">
         <f aca="false">TEXT(G238,"ddd")</f>
@@ -10122,13 +10391,14 @@
         <v>2</v>
       </c>
       <c r="I238" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J238" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K238" s="2"/>
       <c r="L238" s="2"/>
+      <c r="M238" s="4"/>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="2" t="n">
@@ -10142,10 +10412,10 @@
         <v>80</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F239" s="2" t="str">
         <f aca="false">TEXT(G239,"ddd")</f>
@@ -10160,13 +10430,14 @@
         <v>2</v>
       </c>
       <c r="I239" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J239" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K239" s="2"/>
       <c r="L239" s="2"/>
+      <c r="M239" s="4"/>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="2" t="n">
@@ -10180,10 +10451,10 @@
         <v>80</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F240" s="2" t="str">
         <f aca="false">TEXT(G240,"ddd")</f>
@@ -10198,13 +10469,14 @@
         <v>3</v>
       </c>
       <c r="I240" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J240" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K240" s="2"/>
       <c r="L240" s="2"/>
+      <c r="M240" s="4"/>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="2" t="n">
@@ -10218,10 +10490,10 @@
         <v>80</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F241" s="2" t="str">
         <f aca="false">TEXT(G241,"ddd")</f>
@@ -10236,13 +10508,14 @@
         <v>2</v>
       </c>
       <c r="I241" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J241" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K241" s="2"/>
       <c r="L241" s="2"/>
+      <c r="M241" s="4"/>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="2" t="n">
@@ -10256,10 +10529,10 @@
         <v>81</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F242" s="2" t="str">
         <f aca="false">TEXT(G242,"ddd")</f>
@@ -10274,13 +10547,14 @@
         <v>2</v>
       </c>
       <c r="I242" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J242" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K242" s="2"/>
       <c r="L242" s="2"/>
+      <c r="M242" s="4"/>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="2" t="n">
@@ -10294,10 +10568,10 @@
         <v>81</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F243" s="2" t="str">
         <f aca="false">TEXT(G243,"ddd")</f>
@@ -10312,13 +10586,14 @@
         <v>3</v>
       </c>
       <c r="I243" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J243" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K243" s="2"/>
       <c r="L243" s="2"/>
+      <c r="M243" s="4"/>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="2" t="n">
@@ -10332,10 +10607,10 @@
         <v>81</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F244" s="2" t="str">
         <f aca="false">TEXT(G244,"ddd")</f>
@@ -10350,17 +10625,18 @@
         <v>2</v>
       </c>
       <c r="I244" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J244" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K244" s="2"/>
       <c r="L244" s="2"/>
+      <c r="M244" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L244"/>
-  <conditionalFormatting sqref="A2:L244">
+  <autoFilter ref="A1:M244"/>
+  <conditionalFormatting sqref="A2:M244">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>$E2="Reading"</formula>
     </cfRule>
@@ -10649,7 +10925,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -10659,7 +10935,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -10671,20 +10947,20 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B4" s="10" t="n">
         <v>46318</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10697,43 +10973,43 @@
         <v>4</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="11" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10743,13 +11019,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B11" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10759,14 +11035,14 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B14" s="12" t="n">
         <f aca="false">COUNTA(Schedule!A2:A244)</f>
@@ -10776,7 +11052,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B15" s="12" t="n">
         <f aca="false">COUNTIF(Schedule!J2:J244,"Released")</f>
@@ -10786,7 +11062,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B16" s="12" t="n">
         <f aca="false">B14-B15</f>
@@ -10796,7 +11072,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B17" s="13" t="n">
         <f aca="false">MAX(Schedule!G2:G244)</f>
@@ -10806,19 +11082,19 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B18" s="12" t="n">
         <f aca="false">IFERROR(INDEX(Schedule!A2:A244,MATCH(TRUE(),INDEX(Schedule!J2:J244&lt;&gt;"Released",0),0)),"All released")</f>
         <v>2</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B19" s="13" t="n">
         <f aca="false">IFERROR(INDEX(Schedule!G2:G244,B18),"")</f>
@@ -10827,37 +11103,71 @@
       <c r="C19" s="8"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
+      <c r="A20" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="B20" s="12" t="n">
+        <f aca="true">COUNTIFS(Schedule!G2:G244,"&lt;"&amp;TODAY(),Schedule!J2:J244,"&lt;&gt;Released")</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="B21" s="8"/>
+      <c r="A21" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B21" s="12" t="n">
+        <f aca="false">COUNTIF(Schedule!J2:J244,"Ready")+COUNTIF(Schedule!J2:J244,"Scheduled")</f>
+        <v>2</v>
+      </c>
       <c r="C21" s="8"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
+        <v>151</v>
+      </c>
+      <c r="B22" s="14" t="str">
+        <f aca="false">IF(B20&gt;0,"Behind","On track")</f>
+        <v>On track</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="s">
-        <v>149</v>
-      </c>
+      <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="s">
-        <v>150</v>
+      <c r="A24" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/docs/release-schedule.xlsx
+++ b/docs/release-schedule.xlsx
@@ -784,20 +784,22 @@
       </c>
       <c r="J3" s="18" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="K3" s="18" t="inlineStr">
         <is>
-          <t>Passionless, You See the Subtle · Tao Te Ching, Ch. 1</t>
+          <t>Why Trying Harder Makes You Miss What Matters</t>
         </is>
       </c>
       <c r="L3" s="18" t="inlineStr">
         <is>
-          <t>Main teaching: always passionless, observe the subtle; ever intent, observe the apparent; you need both (shorts/tao-ch1-passionless-subtle). Made, awaiting review.</t>
-        </is>
-      </c>
-      <c r="M3" s="23" t="n"/>
+          <t>Main teaching: always passionless, observe the subtle; ever intent, observe the apparent; you need both (shorts/tao-ch1-passionless-subtle). Made, awaiting review.; main teaching: always passionless, observe the subtle; ever intent, observe the apparent</t>
+        </is>
+      </c>
+      <c r="M3" s="23" t="n">
+        <v>46319</v>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="16">
       <c r="A4" s="18" t="n">

--- a/docs/release-schedule.xlsx
+++ b/docs/release-schedule.xlsx
@@ -784,7 +784,7 @@
       </c>
       <c r="J3" s="18" t="inlineStr">
         <is>
-          <t>Ready</t>
+          <t>Released</t>
         </is>
       </c>
       <c r="K3" s="18" t="inlineStr">
@@ -841,12 +841,20 @@
       </c>
       <c r="J4" s="18" t="inlineStr">
         <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="K4" s="18" t="n"/>
-      <c r="L4" s="18" t="n"/>
-      <c r="M4" s="20" t="n"/>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="K4" s="18" t="inlineStr">
+        <is>
+          <t>Turn It Into a Formula and It Loses Its Power</t>
+        </is>
+      </c>
+      <c r="L4" s="18" t="inlineStr">
+        <is>
+          <t>a way can be a guide, not a fixed path</t>
+        </is>
+      </c>
+      <c r="M4" s="23" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="16">
       <c r="A5" s="18" t="n">
